--- a/关键标准答案.xlsx
+++ b/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Rbacd00cb72234b08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Rd701ae8435694fc1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="Ra57b9181863542ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R6bf136e131204526"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R03a9d24ca83a458f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R05ca7a88e7cb48ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R7f0f6faa63ed43cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R42060ef22a2646db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Rd77f7bd8d5f64545"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R38e60d1c443a46b0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -602,41 +602,41 @@
         <x:v>归档月分区</x:v>
       </x:c>
       <x:c r="B2" s="5" t="str">
-        <x:v>month_start早于detach_before的库存分区</x:v>
+        <x:v>notification_events_2026_01、notification_events_2026_02、notification_events_2026_03</x:v>
       </x:c>
       <x:c r="C2" s="5" t="str">
         <x:v>按partition_name无序比较</x:v>
       </x:c>
       <x:c r="D2" s="5" t="str">
-        <x:v>partition_inventory.csv与retention_policy.json</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="48" customHeight="1">
+        <x:v>分区库存与保留策略</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="63" customHeight="1">
       <x:c r="A3" s="5" t="str">
         <x:v>活动月分区</x:v>
       </x:c>
       <x:c r="B3" s="5" t="str">
-        <x:v>month_start位于保留区间的库存分区</x:v>
+        <x:v>notification_events_2026_04、notification_events_2026_05、notification_events_2026_06、notification_events_2026_07</x:v>
       </x:c>
       <x:c r="C3" s="5" t="str">
         <x:v>按partition_name无序比较</x:v>
       </x:c>
       <x:c r="D3" s="5" t="str">
-        <x:v>partition_inventory.csv与retention_policy.json</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="33" customHeight="1">
+        <x:v>分区库存与保留策略</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="78" customHeight="1">
       <x:c r="A4" s="5" t="str">
         <x:v>索引交接对象</x:v>
       </x:c>
       <x:c r="B4" s="5" t="str">
-        <x:v>全部活动月分区加默认分区</x:v>
+        <x:v>notification_events_2026_04、notification_events_2026_05、notification_events_2026_06、notification_events_2026_07、notification_events_default</x:v>
       </x:c>
       <x:c r="C4" s="5" t="str">
         <x:v>按partition_name无序比较</x:v>
       </x:c>
       <x:c r="D4" s="5" t="str">
-        <x:v>保留区间与默认分区</x:v>
+        <x:v>index_handover.csv</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="33" customHeight="1">
@@ -644,13 +644,13 @@
         <x:v>租户审计对象</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
-        <x:v>tenant_monthly_capacity.csv中的tenant_id</x:v>
+        <x:v>TENANT-A、TENANT-B、TENANT-C</x:v>
       </x:c>
       <x:c r="C5" s="5" t="str">
         <x:v>按tenant_id无序比较</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
-        <x:v>租户月度容量快照</x:v>
+        <x:v>tenant_retention_audit.csv</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="48" customHeight="1">
@@ -706,7 +706,7 @@
         <x:v>指标</x:v>
       </x:c>
       <x:c r="C1" s="9" t="str">
-        <x:v>计算方式</x:v>
+        <x:v>正确值</x:v>
       </x:c>
       <x:c r="D1" s="9" t="str">
         <x:v>单位</x:v>
@@ -725,8 +725,8 @@
       <x:c r="B2" s="5" t="str">
         <x:v>月分区数量</x:v>
       </x:c>
-      <x:c r="C2" s="5" t="str">
-        <x:v>partition_inventory.csv数据行数</x:v>
+      <x:c r="C2" s="5" t="n">
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D2" s="5" t="str">
         <x:v>个</x:v>
@@ -735,7 +735,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2" s="5" t="str">
-        <x:v>分区库存</x:v>
+        <x:v>partition_inventory.csv</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="33" customHeight="1">
@@ -745,8 +745,8 @@
       <x:c r="B3" s="5" t="str">
         <x:v>归档分区数量</x:v>
       </x:c>
-      <x:c r="C3" s="5" t="str">
-        <x:v>month_start早于detach_before的分区数量</x:v>
+      <x:c r="C3" s="5" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D3" s="5" t="str">
         <x:v>个</x:v>
@@ -755,7 +755,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3" s="5" t="str">
-        <x:v>保留策略与分区库存</x:v>
+        <x:v>change_handover.json</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="33" customHeight="1">
@@ -765,8 +765,8 @@
       <x:c r="B4" s="5" t="str">
         <x:v>archived_reported_rows</x:v>
       </x:c>
-      <x:c r="C4" s="5" t="str">
-        <x:v>归档月reported_rows求和</x:v>
+      <x:c r="C4" s="5" t="n">
+        <x:v>360000</x:v>
       </x:c>
       <x:c r="D4" s="5" t="str">
         <x:v>行</x:v>
@@ -775,7 +775,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F4" s="5" t="str">
-        <x:v>分区库存与归档登记</x:v>
+        <x:v>change_handover.json</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="33" customHeight="1">
@@ -785,8 +785,8 @@
       <x:c r="B5" s="5" t="str">
         <x:v>retained_reported_rows</x:v>
       </x:c>
-      <x:c r="C5" s="5" t="str">
-        <x:v>活动月reported_rows求和</x:v>
+      <x:c r="C5" s="5" t="n">
+        <x:v>520000</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
         <x:v>行</x:v>
@@ -795,7 +795,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="5" t="str">
-        <x:v>分区库存与保留策略</x:v>
+        <x:v>change_handover.json</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="33" customHeight="1">
@@ -805,8 +805,8 @@
       <x:c r="B6" s="5" t="str">
         <x:v>retained_failed_rows</x:v>
       </x:c>
-      <x:c r="C6" s="5" t="str">
-        <x:v>活动月reported_failed_rows求和</x:v>
+      <x:c r="C6" s="5" t="n">
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D6" s="5" t="str">
         <x:v>行</x:v>
@@ -815,18 +815,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F6" s="5" t="str">
-        <x:v>分区库存与保留策略</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="33" customHeight="1">
+        <x:v>change_handover.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="48" customHeight="1">
       <x:c r="A7" s="5" t="str">
-        <x:v>租户审计</x:v>
+        <x:v>TENANT-A</x:v>
       </x:c>
       <x:c r="B7" s="5" t="str">
-        <x:v>archived_rows</x:v>
+        <x:v>archived_rows、retained_rows、retained_failed_rows</x:v>
       </x:c>
       <x:c r="C7" s="5" t="str">
-        <x:v>按tenant_id汇总归档月reported_rows</x:v>
+        <x:v>128000、182000、4500</x:v>
       </x:c>
       <x:c r="D7" s="5" t="str">
         <x:v>行</x:v>
@@ -835,18 +835,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F7" s="5" t="str">
-        <x:v>租户月度容量与保留策略</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="33" customHeight="1">
+        <x:v>tenant_retention_audit.csv</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="48" customHeight="1">
       <x:c r="A8" s="5" t="str">
-        <x:v>租户审计</x:v>
+        <x:v>TENANT-B</x:v>
       </x:c>
       <x:c r="B8" s="5" t="str">
-        <x:v>retained_rows</x:v>
+        <x:v>archived_rows、retained_rows、retained_failed_rows</x:v>
       </x:c>
       <x:c r="C8" s="5" t="str">
-        <x:v>按tenant_id汇总活动月reported_rows</x:v>
+        <x:v>120000、174000、4300</x:v>
       </x:c>
       <x:c r="D8" s="5" t="str">
         <x:v>行</x:v>
@@ -855,18 +855,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F8" s="5" t="str">
-        <x:v>租户月度容量与保留策略</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="33" customHeight="1">
+        <x:v>tenant_retention_audit.csv</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="48" customHeight="1">
       <x:c r="A9" s="5" t="str">
-        <x:v>租户审计</x:v>
+        <x:v>TENANT-C</x:v>
       </x:c>
       <x:c r="B9" s="5" t="str">
-        <x:v>retained_failed_rows</x:v>
+        <x:v>archived_rows、retained_rows、retained_failed_rows</x:v>
       </x:c>
       <x:c r="C9" s="5" t="str">
-        <x:v>按tenant_id汇总活动月reported_failed_rows</x:v>
+        <x:v>112000、164000、4200</x:v>
       </x:c>
       <x:c r="D9" s="5" t="str">
         <x:v>行</x:v>
@@ -875,7 +875,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F9" s="5" t="str">
-        <x:v>租户月度容量与保留策略</x:v>
+        <x:v>tenant_retention_audit.csv</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="33" customHeight="1">
@@ -885,8 +885,8 @@
       <x:c r="B10" s="5" t="str">
         <x:v>child_indexes_attached</x:v>
       </x:c>
-      <x:c r="C10" s="5" t="str">
-        <x:v>活动月分区数量加默认分区</x:v>
+      <x:c r="C10" s="5" t="n">
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D10" s="5" t="str">
         <x:v>个</x:v>
@@ -895,27 +895,67 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F10" s="5" t="str">
-        <x:v>pg_inherits与保留区间</x:v>
+        <x:v>change_handover.json</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="33" customHeight="1">
       <x:c r="A11" s="5" t="str">
+        <x:v>索引交接</x:v>
+      </x:c>
+      <x:c r="B11" s="5" t="str">
+        <x:v>legacy_indexes_removed</x:v>
+      </x:c>
+      <x:c r="C11" s="5" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D11" s="5" t="str">
+        <x:v>个</x:v>
+      </x:c>
+      <x:c r="E11" s="5" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F11" s="5" t="str">
+        <x:v>change_handover.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="48" customHeight="1">
+      <x:c r="A12" s="5" t="str">
         <x:v>业务文件</x:v>
       </x:c>
-      <x:c r="B11" s="5" t="str">
-        <x:v>delivery_rows</x:v>
-      </x:c>
-      <x:c r="C11" s="5" t="str">
-        <x:v>分别统计三份CSV的数据行数</x:v>
-      </x:c>
-      <x:c r="D11" s="5" t="str">
+      <x:c r="B12" s="5" t="str">
+        <x:v>partition_action_plan、index_handover、tenant_retention_audit</x:v>
+      </x:c>
+      <x:c r="C12" s="5" t="str">
+        <x:v>8、5、3</x:v>
+      </x:c>
+      <x:c r="D12" s="5" t="str">
         <x:v>行</x:v>
       </x:c>
-      <x:c r="E11" s="5" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F11" s="5" t="str">
-        <x:v>当前数据库查询</x:v>
+      <x:c r="E12" s="5" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F12" s="5" t="str">
+        <x:v>change_handover.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="48" customHeight="1">
+      <x:c r="A13" s="5" t="str">
+        <x:v>输入载入</x:v>
+      </x:c>
+      <x:c r="B13" s="5" t="str">
+        <x:v>partition_inventory、tenant_monthly_capacity、notification_events</x:v>
+      </x:c>
+      <x:c r="C13" s="5" t="str">
+        <x:v>7、21、14</x:v>
+      </x:c>
+      <x:c r="D13" s="5" t="str">
+        <x:v>行</x:v>
+      </x:c>
+      <x:c r="E13" s="5" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F13" s="5" t="str">
+        <x:v>change_handover.json</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/关键标准答案.xlsx
+++ b/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R05ca7a88e7cb48ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R7f0f6faa63ed43cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R42060ef22a2646db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Rd77f7bd8d5f64545"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R38e60d1c443a46b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R4780fd719a5745d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Ra8594d6c51f74128"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R4a6ae4d2ac3046c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R59de7b30b8dc47c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Rc2f5e4c3ac484878"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -320,7 +320,7 @@
         <x:v>交付物名称</x:v>
       </x:c>
       <x:c r="B1" s="9" t="str">
-        <x:v>固定路径</x:v>
+        <x:v>固定路径/命名规则</x:v>
       </x:c>
       <x:c r="C1" s="9" t="str">
         <x:v>格式</x:v>
